--- a/main/java/hospitaldatabase/activepatient.xlsx
+++ b/main/java/hospitaldatabase/activepatient.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>FirstName</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>SIMON</t>
+  </si>
+  <si>
+    <t>johnson</t>
+  </si>
+  <si>
+    <t>HIV</t>
   </si>
 </sst>
 </file>
@@ -171,10 +177,10 @@
         <v>19</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>251.02</v>
+        <v>250.01</v>
       </c>
     </row>
   </sheetData>

--- a/main/java/hospitaldatabase/activepatient.xlsx
+++ b/main/java/hospitaldatabase/activepatient.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
   <si>
     <t>FirstName</t>
   </si>
@@ -41,6 +41,9 @@
     <t>Outstandingbill</t>
   </si>
   <si>
+    <t>AssignedWardName</t>
+  </si>
+  <si>
     <t>james</t>
   </si>
   <si>
@@ -59,25 +62,34 @@
     <t>typhoid</t>
   </si>
   <si>
-    <t>SOPHIA</t>
-  </si>
-  <si>
-    <t>BETTY</t>
-  </si>
-  <si>
-    <t>DINE</t>
+    <t>purple</t>
+  </si>
+  <si>
+    <t>abel</t>
+  </si>
+  <si>
+    <t>cynthia</t>
+  </si>
+  <si>
+    <t>favour</t>
   </si>
   <si>
     <t>Female</t>
   </si>
   <si>
-    <t>SIMON</t>
-  </si>
-  <si>
-    <t>johnson</t>
-  </si>
-  <si>
-    <t>HIV</t>
+    <t>kate</t>
+  </si>
+  <si>
+    <t>david</t>
+  </si>
+  <si>
+    <t>sophia</t>
+  </si>
+  <si>
+    <t>iglofi</t>
+  </si>
+  <si>
+    <t>soa</t>
   </si>
 </sst>
 </file>
@@ -122,7 +134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -153,34 +165,136 @@
       <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
+      <c r="J1" t="s" s="0">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="G2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>251.02</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="D3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="G3" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="n" s="0">
-        <v>250.01</v>
+      <c r="H3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>251.02</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>251.02</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>292.02</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
